--- a/Recherche_stage_briantoAlexandre.xlsx
+++ b/Recherche_stage_briantoAlexandre.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
   <si>
     <t xml:space="preserve">NOM :</t>
   </si>
@@ -90,6 +90,9 @@
     <t xml:space="preserve">Lien vers candidature</t>
   </si>
   <si>
+    <t xml:space="preserve">Lieu</t>
+  </si>
+  <si>
     <t xml:space="preserve">Delta Evo</t>
   </si>
   <si>
@@ -132,13 +135,34 @@
     <t xml:space="preserve">e.bregnard@courtepaille.com</t>
   </si>
   <si>
+    <t xml:space="preserve">x</t>
+  </si>
+  <si>
     <t xml:space="preserve">t.gouars@courtepaille.com</t>
   </si>
   <si>
     <t xml:space="preserve">Thales (91883 Massy)</t>
   </si>
   <si>
+    <t xml:space="preserve">Refus</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://fr.indeed.com/jobs?q=thales+stage+python&amp;l=melun&amp;radius=25&amp;from=searchOnDesktopSerp&amp;vjk=ab997cb60d5b5340 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingénieur-e Développement Méthodes &amp; Outils en Aérothermique et Thermomécanique F/H - Safran Aircraft Engines - Autres à Moissy-Cramayel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eleven Lab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Développeur(se) Python Senior(e) F/H/X - Eleven Labs - CDI à Paris </t>
+  </si>
+  <si>
+    <t xml:space="preserve">102 Rue du Faubourg Saint-Honoré - Google Maps </t>
   </si>
   <si>
     <t xml:space="preserve">positive</t>
@@ -283,7 +307,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -334,6 +358,10 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -448,9 +476,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>16200</xdr:colOff>
+      <xdr:colOff>15480</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>179280</xdr:rowOff>
+      <xdr:rowOff>178560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -460,7 +488,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7990200" y="0"/>
-          <a:ext cx="7823520" cy="1512720"/>
+          <a:ext cx="7822800" cy="1512000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -627,7 +655,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="21.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="18.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="24.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="149.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="149.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="92.3"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -711,25 +740,28 @@
       <c r="J10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="0" t="s">
+      <c r="K10" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="L10" s="0" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>45870</v>
@@ -744,21 +776,21 @@
         <v>45897</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>45945</v>
@@ -769,96 +801,127 @@
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
       <c r="J12" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>46068</v>
       </c>
-      <c r="G13" s="9"/>
+      <c r="G13" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>46068</v>
       </c>
-      <c r="G14" s="9"/>
+      <c r="G14" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
       <c r="J14" s="9"/>
     </row>
     <row r="15" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="8"/>
       <c r="E15" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>46080</v>
       </c>
-      <c r="G15" s="9"/>
+      <c r="G15" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
       <c r="K15" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="C16" s="6"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
+      <c r="E16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>46130</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="H16" s="9"/>
       <c r="I16" s="9"/>
       <c r="J16" s="9"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K16" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="C17" s="6"/>
       <c r="D17" s="8"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="9"/>
+      <c r="E17" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>46138</v>
+      </c>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
+      <c r="K17" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="6"/>
@@ -3475,6 +3538,9 @@
     <hyperlink ref="B5" r:id="rId1" display="alexandre.brianto29@gmail.com"/>
     <hyperlink ref="B6" r:id="rId2" display="https://briantoalexandre.github.io"/>
     <hyperlink ref="D11" r:id="rId3" display="jcm.delta@deltaevo.com"/>
+    <hyperlink ref="K16" r:id="rId4" display="Ingénieur-e Développement Méthodes &amp; Outils en Aérothermique et Thermomécanique F/H - Safran Aircraft Engines - Autres à Moissy-Cramayel "/>
+    <hyperlink ref="K17" r:id="rId5" display="Développeur(se) Python Senior(e) F/H/X - Eleven Labs - CDI à Paris"/>
+    <hyperlink ref="L17" r:id="rId6" display="102 Rue du Faubourg Saint-Honoré - Google Maps"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3483,9 +3549,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId4"/>
+  <drawing r:id="rId7"/>
   <tableParts>
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId8"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3500,27 +3566,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Recherche_stage_briantoAlexandre.xlsx
+++ b/Recherche_stage_briantoAlexandre.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="51">
   <si>
     <t xml:space="preserve">NOM :</t>
   </si>
@@ -156,13 +156,22 @@
     <t xml:space="preserve">Ingénieur-e Développement Méthodes &amp; Outils en Aérothermique et Thermomécanique F/H - Safran Aircraft Engines - Autres à Moissy-Cramayel </t>
   </si>
   <si>
-    <t xml:space="preserve">Eleven Lab</t>
+    <t xml:space="preserve">Eleven Labs</t>
   </si>
   <si>
     <t xml:space="preserve">Développeur(se) Python Senior(e) F/H/X - Eleven Labs - CDI à Paris </t>
   </si>
   <si>
     <t xml:space="preserve">102 Rue du Faubourg Saint-Honoré - Google Maps </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job Link Group </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Développeur Python/Django F/H - Job Link Group - CDI à La Défense </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Maps </t>
   </si>
   <si>
     <t xml:space="preserve">positive</t>
@@ -476,9 +485,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>15480</xdr:colOff>
+      <xdr:colOff>14760</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>178560</xdr:rowOff>
+      <xdr:rowOff>177840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -488,7 +497,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7990200" y="0"/>
-          <a:ext cx="7822800" cy="1512000"/>
+          <a:ext cx="7822080" cy="1511280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -656,7 +665,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="18.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="24.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="149.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="92.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="92.3"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -743,7 +752,7 @@
       <c r="K10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L10" s="0" t="s">
+      <c r="L10" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -916,22 +925,35 @@
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
-      <c r="K17" s="14" t="s">
+      <c r="K17" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="L17" s="14" t="s">
+      <c r="L17" s="13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
+        <v>46</v>
+      </c>
       <c r="C18" s="6"/>
       <c r="D18" s="8"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="9"/>
+      <c r="E18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>46138</v>
+      </c>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
+      <c r="K18" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="L18" s="14" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="6"/>
@@ -3539,8 +3561,11 @@
     <hyperlink ref="B6" r:id="rId2" display="https://briantoalexandre.github.io"/>
     <hyperlink ref="D11" r:id="rId3" display="jcm.delta@deltaevo.com"/>
     <hyperlink ref="K16" r:id="rId4" display="Ingénieur-e Développement Méthodes &amp; Outils en Aérothermique et Thermomécanique F/H - Safran Aircraft Engines - Autres à Moissy-Cramayel "/>
-    <hyperlink ref="K17" r:id="rId5" display="Développeur(se) Python Senior(e) F/H/X - Eleven Labs - CDI à Paris"/>
-    <hyperlink ref="L17" r:id="rId6" display="102 Rue du Faubourg Saint-Honoré - Google Maps"/>
+    <hyperlink ref="K17" r:id="rId5" display="Développeur(se) Python Senior(e) F/H/X - Eleven Labs - CDI à Paris "/>
+    <hyperlink ref="L17" r:id="rId6" display="102 Rue du Faubourg Saint-Honoré - Google Maps "/>
+    <hyperlink ref="A18" r:id="rId7" display="Job Link Group"/>
+    <hyperlink ref="K18" r:id="rId8" display="Développeur Python/Django F/H - Job Link Group - CDI à La Défense"/>
+    <hyperlink ref="L18" r:id="rId9" display="Google Maps"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3549,9 +3574,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId7"/>
+  <drawing r:id="rId10"/>
   <tableParts>
-    <tablePart r:id="rId8"/>
+    <tablePart r:id="rId11"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3576,12 +3601,12 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
